--- a/smartshop/EvidenceBasedAdaptiveUI/reports/DefaultUI/mobile_defaults.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/DefaultUI/mobile_defaults.xlsx
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>47</v>
+        <v>48.21</v>
       </c>
       <c r="D2" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="E2" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
@@ -496,13 +496,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>68.5</v>
+        <v>68.3</v>
       </c>
       <c r="D3" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E3" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83</v>
+        <v>82.59</v>
       </c>
       <c r="D4" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="E4" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>85</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="E5" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>50.45</v>
       </c>
       <c r="D6" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E6" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>39.5</v>
+        <v>40.18</v>
       </c>
       <c r="D7" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E7" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -616,13 +616,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>42.5</v>
+        <v>43.75</v>
       </c>
       <c r="D8" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="E8" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>39</v>
+        <v>39.73</v>
       </c>
       <c r="D9" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E9" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
@@ -664,13 +664,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>62.5</v>
+        <v>60.71</v>
       </c>
       <c r="D10" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E10" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>58</v>
+        <v>58.48</v>
       </c>
       <c r="D11" t="n">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="E11" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>53.57</v>
       </c>
       <c r="D12" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="E12" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>54.46</v>
       </c>
       <c r="D13" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="E13" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>64.5</v>
+        <v>65.62</v>
       </c>
       <c r="D14" t="n">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="E14" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
@@ -784,13 +784,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55.5</v>
+        <v>54.91</v>
       </c>
       <c r="D15" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="E15" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
